--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D92323-BAF7-4B5E-B9FF-02433DA43819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2704A86-BF7B-4C73-BDF4-A433010F241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47640" yWindow="2145" windowWidth="16635" windowHeight="12870" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -205,6 +205,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -511,22 +512,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="84.5546875" customWidth="1"/>
+    <col min="2" max="2" width="84.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,35 +535,35 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
     </row>
   </sheetData>
@@ -576,14 +577,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -677,68 +678,8 @@
       <c r="AE1" s="3">
         <v>2050</v>
       </c>
-      <c r="AF1" s="3">
-        <v>2051</v>
-      </c>
-      <c r="AG1" s="3">
-        <v>2052</v>
-      </c>
-      <c r="AH1" s="3">
-        <v>2053</v>
-      </c>
-      <c r="AI1" s="3">
-        <v>2054</v>
-      </c>
-      <c r="AJ1" s="3">
-        <v>2055</v>
-      </c>
-      <c r="AK1" s="3">
-        <v>2056</v>
-      </c>
-      <c r="AL1" s="3">
-        <v>2057</v>
-      </c>
-      <c r="AM1" s="3">
-        <v>2058</v>
-      </c>
-      <c r="AN1" s="3">
-        <v>2059</v>
-      </c>
-      <c r="AO1" s="3">
-        <v>2060</v>
-      </c>
-      <c r="AP1" s="3">
-        <v>2061</v>
-      </c>
-      <c r="AQ1" s="3">
-        <v>2062</v>
-      </c>
-      <c r="AR1" s="3">
-        <v>2063</v>
-      </c>
-      <c r="AS1" s="3">
-        <v>2064</v>
-      </c>
-      <c r="AT1" s="3">
-        <v>2065</v>
-      </c>
-      <c r="AU1" s="3">
-        <v>2066</v>
-      </c>
-      <c r="AV1" s="3">
-        <v>2067</v>
-      </c>
-      <c r="AW1" s="3">
-        <v>2068</v>
-      </c>
-      <c r="AX1" s="3">
-        <v>2069</v>
-      </c>
-      <c r="AY1" s="3">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -832,68 +773,8 @@
       <c r="AE2">
         <v>0</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -987,68 +868,8 @@
       <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1142,68 +963,8 @@
       <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1297,68 +1058,8 @@
       <c r="AE5">
         <v>1</v>
       </c>
-      <c r="AF5">
-        <v>1</v>
-      </c>
-      <c r="AG5">
-        <v>1</v>
-      </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <v>1</v>
-      </c>
-      <c r="AJ5">
-        <v>1</v>
-      </c>
-      <c r="AK5">
-        <v>1</v>
-      </c>
-      <c r="AL5">
-        <v>1</v>
-      </c>
-      <c r="AM5">
-        <v>1</v>
-      </c>
-      <c r="AN5">
-        <v>1</v>
-      </c>
-      <c r="AO5">
-        <v>1</v>
-      </c>
-      <c r="AP5">
-        <v>1</v>
-      </c>
-      <c r="AQ5">
-        <v>1</v>
-      </c>
-      <c r="AR5">
-        <v>1</v>
-      </c>
-      <c r="AS5">
-        <v>1</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>1</v>
-      </c>
-      <c r="AV5">
-        <v>1</v>
-      </c>
-      <c r="AW5">
-        <v>1</v>
-      </c>
-      <c r="AX5">
-        <v>1</v>
-      </c>
-      <c r="AY5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1452,68 +1153,8 @@
       <c r="AE6">
         <v>1</v>
       </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AG6">
-        <v>1</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6">
-        <v>1</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AM6">
-        <v>1</v>
-      </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
-      <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6">
-        <v>1</v>
-      </c>
-      <c r="AR6">
-        <v>1</v>
-      </c>
-      <c r="AS6">
-        <v>1</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>1</v>
-      </c>
-      <c r="AV6">
-        <v>1</v>
-      </c>
-      <c r="AW6">
-        <v>1</v>
-      </c>
-      <c r="AX6">
-        <v>1</v>
-      </c>
-      <c r="AY6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1607,68 +1248,8 @@
       <c r="AE7">
         <v>1</v>
       </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AG7">
-        <v>1</v>
-      </c>
-      <c r="AH7">
-        <v>1</v>
-      </c>
-      <c r="AI7">
-        <v>1</v>
-      </c>
-      <c r="AJ7">
-        <v>1</v>
-      </c>
-      <c r="AK7">
-        <v>1</v>
-      </c>
-      <c r="AL7">
-        <v>1</v>
-      </c>
-      <c r="AM7">
-        <v>1</v>
-      </c>
-      <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7">
-        <v>1</v>
-      </c>
-      <c r="AP7">
-        <v>1</v>
-      </c>
-      <c r="AQ7">
-        <v>1</v>
-      </c>
-      <c r="AR7">
-        <v>1</v>
-      </c>
-      <c r="AS7">
-        <v>1</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>1</v>
-      </c>
-      <c r="AV7">
-        <v>1</v>
-      </c>
-      <c r="AW7">
-        <v>1</v>
-      </c>
-      <c r="AX7">
-        <v>1</v>
-      </c>
-      <c r="AY7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1762,68 +1343,8 @@
       <c r="AE8">
         <v>1</v>
       </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-      <c r="AH8">
-        <v>1</v>
-      </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-      <c r="AJ8">
-        <v>1</v>
-      </c>
-      <c r="AK8">
-        <v>1</v>
-      </c>
-      <c r="AL8">
-        <v>1</v>
-      </c>
-      <c r="AM8">
-        <v>1</v>
-      </c>
-      <c r="AN8">
-        <v>1</v>
-      </c>
-      <c r="AO8">
-        <v>1</v>
-      </c>
-      <c r="AP8">
-        <v>1</v>
-      </c>
-      <c r="AQ8">
-        <v>1</v>
-      </c>
-      <c r="AR8">
-        <v>1</v>
-      </c>
-      <c r="AS8">
-        <v>1</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-      <c r="AV8">
-        <v>1</v>
-      </c>
-      <c r="AW8">
-        <v>1</v>
-      </c>
-      <c r="AX8">
-        <v>1</v>
-      </c>
-      <c r="AY8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1917,68 +1438,8 @@
       <c r="AE9">
         <v>1</v>
       </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-      <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9">
-        <v>1</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
-      <c r="AK9">
-        <v>1</v>
-      </c>
-      <c r="AL9">
-        <v>1</v>
-      </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AN9">
-        <v>1</v>
-      </c>
-      <c r="AO9">
-        <v>1</v>
-      </c>
-      <c r="AP9">
-        <v>1</v>
-      </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
-      <c r="AR9">
-        <v>1</v>
-      </c>
-      <c r="AS9">
-        <v>1</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>1</v>
-      </c>
-      <c r="AV9">
-        <v>1</v>
-      </c>
-      <c r="AW9">
-        <v>1</v>
-      </c>
-      <c r="AX9">
-        <v>1</v>
-      </c>
-      <c r="AY9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2072,68 +1533,8 @@
       <c r="AE10">
         <v>1</v>
       </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
-      <c r="AG10">
-        <v>1</v>
-      </c>
-      <c r="AH10">
-        <v>1</v>
-      </c>
-      <c r="AI10">
-        <v>1</v>
-      </c>
-      <c r="AJ10">
-        <v>1</v>
-      </c>
-      <c r="AK10">
-        <v>1</v>
-      </c>
-      <c r="AL10">
-        <v>1</v>
-      </c>
-      <c r="AM10">
-        <v>1</v>
-      </c>
-      <c r="AN10">
-        <v>1</v>
-      </c>
-      <c r="AO10">
-        <v>1</v>
-      </c>
-      <c r="AP10">
-        <v>1</v>
-      </c>
-      <c r="AQ10">
-        <v>1</v>
-      </c>
-      <c r="AR10">
-        <v>1</v>
-      </c>
-      <c r="AS10">
-        <v>1</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>1</v>
-      </c>
-      <c r="AV10">
-        <v>1</v>
-      </c>
-      <c r="AW10">
-        <v>1</v>
-      </c>
-      <c r="AX10">
-        <v>1</v>
-      </c>
-      <c r="AY10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2227,68 +1628,8 @@
       <c r="AE11">
         <v>1</v>
       </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-      <c r="AH11">
-        <v>1</v>
-      </c>
-      <c r="AI11">
-        <v>1</v>
-      </c>
-      <c r="AJ11">
-        <v>1</v>
-      </c>
-      <c r="AK11">
-        <v>1</v>
-      </c>
-      <c r="AL11">
-        <v>1</v>
-      </c>
-      <c r="AM11">
-        <v>1</v>
-      </c>
-      <c r="AN11">
-        <v>1</v>
-      </c>
-      <c r="AO11">
-        <v>1</v>
-      </c>
-      <c r="AP11">
-        <v>1</v>
-      </c>
-      <c r="AQ11">
-        <v>1</v>
-      </c>
-      <c r="AR11">
-        <v>1</v>
-      </c>
-      <c r="AS11">
-        <v>1</v>
-      </c>
-      <c r="AT11">
-        <v>1</v>
-      </c>
-      <c r="AU11">
-        <v>1</v>
-      </c>
-      <c r="AV11">
-        <v>1</v>
-      </c>
-      <c r="AW11">
-        <v>1</v>
-      </c>
-      <c r="AX11">
-        <v>1</v>
-      </c>
-      <c r="AY11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2382,68 +1723,8 @@
       <c r="AE12">
         <v>0</v>
       </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2537,68 +1818,8 @@
       <c r="AE13">
         <v>0</v>
       </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2607,154 +1828,123 @@
         <v>0</v>
       </c>
       <c r="C14">
+        <f t="shared" ref="C14:AE14" si="0">C2</f>
         <v>0</v>
       </c>
       <c r="D14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2848,68 +2038,8 @@
       <c r="AE15">
         <v>1</v>
       </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>1</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
-      <c r="AK15">
-        <v>1</v>
-      </c>
-      <c r="AL15">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>1</v>
-      </c>
-      <c r="AN15">
-        <v>1</v>
-      </c>
-      <c r="AO15">
-        <v>1</v>
-      </c>
-      <c r="AP15">
-        <v>1</v>
-      </c>
-      <c r="AQ15">
-        <v>1</v>
-      </c>
-      <c r="AR15">
-        <v>1</v>
-      </c>
-      <c r="AS15">
-        <v>1</v>
-      </c>
-      <c r="AT15">
-        <v>1</v>
-      </c>
-      <c r="AU15">
-        <v>1</v>
-      </c>
-      <c r="AV15">
-        <v>1</v>
-      </c>
-      <c r="AW15">
-        <v>1</v>
-      </c>
-      <c r="AX15">
-        <v>1</v>
-      </c>
-      <c r="AY15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -3003,68 +2133,8 @@
       <c r="AE16">
         <v>0</v>
       </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -3158,223 +2228,103 @@
       <c r="AE17">
         <v>0</v>
       </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <v>1</v>
-      </c>
-      <c r="AG18">
-        <v>1</v>
-      </c>
-      <c r="AH18">
-        <v>1</v>
-      </c>
-      <c r="AI18">
-        <v>1</v>
-      </c>
-      <c r="AJ18">
-        <v>1</v>
-      </c>
-      <c r="AK18">
-        <v>1</v>
-      </c>
-      <c r="AL18">
-        <v>1</v>
-      </c>
-      <c r="AM18">
-        <v>1</v>
-      </c>
-      <c r="AN18">
-        <v>1</v>
-      </c>
-      <c r="AO18">
-        <v>1</v>
-      </c>
-      <c r="AP18">
-        <v>1</v>
-      </c>
-      <c r="AQ18">
-        <v>1</v>
-      </c>
-      <c r="AR18">
-        <v>1</v>
-      </c>
-      <c r="AS18">
-        <v>1</v>
-      </c>
-      <c r="AT18">
-        <v>1</v>
-      </c>
-      <c r="AU18">
-        <v>1</v>
-      </c>
-      <c r="AV18">
-        <v>1</v>
-      </c>
-      <c r="AW18">
-        <v>1</v>
-      </c>
-      <c r="AX18">
-        <v>1</v>
-      </c>
-      <c r="AY18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -3468,68 +2418,8 @@
       <c r="AE19">
         <v>1</v>
       </c>
-      <c r="AF19">
-        <v>1</v>
-      </c>
-      <c r="AG19">
-        <v>1</v>
-      </c>
-      <c r="AH19">
-        <v>1</v>
-      </c>
-      <c r="AI19">
-        <v>1</v>
-      </c>
-      <c r="AJ19">
-        <v>1</v>
-      </c>
-      <c r="AK19">
-        <v>1</v>
-      </c>
-      <c r="AL19">
-        <v>1</v>
-      </c>
-      <c r="AM19">
-        <v>1</v>
-      </c>
-      <c r="AN19">
-        <v>1</v>
-      </c>
-      <c r="AO19">
-        <v>1</v>
-      </c>
-      <c r="AP19">
-        <v>1</v>
-      </c>
-      <c r="AQ19">
-        <v>1</v>
-      </c>
-      <c r="AR19">
-        <v>1</v>
-      </c>
-      <c r="AS19">
-        <v>1</v>
-      </c>
-      <c r="AT19">
-        <v>1</v>
-      </c>
-      <c r="AU19">
-        <v>1</v>
-      </c>
-      <c r="AV19">
-        <v>1</v>
-      </c>
-      <c r="AW19">
-        <v>1</v>
-      </c>
-      <c r="AX19">
-        <v>1</v>
-      </c>
-      <c r="AY19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -3623,68 +2513,8 @@
       <c r="AE20">
         <v>1</v>
       </c>
-      <c r="AF20">
-        <v>1</v>
-      </c>
-      <c r="AG20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>1</v>
-      </c>
-      <c r="AI20">
-        <v>1</v>
-      </c>
-      <c r="AJ20">
-        <v>1</v>
-      </c>
-      <c r="AK20">
-        <v>1</v>
-      </c>
-      <c r="AL20">
-        <v>1</v>
-      </c>
-      <c r="AM20">
-        <v>1</v>
-      </c>
-      <c r="AN20">
-        <v>1</v>
-      </c>
-      <c r="AO20">
-        <v>1</v>
-      </c>
-      <c r="AP20">
-        <v>1</v>
-      </c>
-      <c r="AQ20">
-        <v>1</v>
-      </c>
-      <c r="AR20">
-        <v>1</v>
-      </c>
-      <c r="AS20">
-        <v>1</v>
-      </c>
-      <c r="AT20">
-        <v>1</v>
-      </c>
-      <c r="AU20">
-        <v>1</v>
-      </c>
-      <c r="AV20">
-        <v>1</v>
-      </c>
-      <c r="AW20">
-        <v>1</v>
-      </c>
-      <c r="AX20">
-        <v>1</v>
-      </c>
-      <c r="AY20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -3778,68 +2608,8 @@
       <c r="AE21">
         <v>1</v>
       </c>
-      <c r="AF21">
-        <v>1</v>
-      </c>
-      <c r="AG21">
-        <v>1</v>
-      </c>
-      <c r="AH21">
-        <v>1</v>
-      </c>
-      <c r="AI21">
-        <v>1</v>
-      </c>
-      <c r="AJ21">
-        <v>1</v>
-      </c>
-      <c r="AK21">
-        <v>1</v>
-      </c>
-      <c r="AL21">
-        <v>1</v>
-      </c>
-      <c r="AM21">
-        <v>1</v>
-      </c>
-      <c r="AN21">
-        <v>1</v>
-      </c>
-      <c r="AO21">
-        <v>1</v>
-      </c>
-      <c r="AP21">
-        <v>1</v>
-      </c>
-      <c r="AQ21">
-        <v>1</v>
-      </c>
-      <c r="AR21">
-        <v>1</v>
-      </c>
-      <c r="AS21">
-        <v>1</v>
-      </c>
-      <c r="AT21">
-        <v>1</v>
-      </c>
-      <c r="AU21">
-        <v>1</v>
-      </c>
-      <c r="AV21">
-        <v>1</v>
-      </c>
-      <c r="AW21">
-        <v>1</v>
-      </c>
-      <c r="AX21">
-        <v>1</v>
-      </c>
-      <c r="AY21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -3933,68 +2703,8 @@
       <c r="AE22">
         <v>1</v>
       </c>
-      <c r="AF22">
-        <v>1</v>
-      </c>
-      <c r="AG22">
-        <v>1</v>
-      </c>
-      <c r="AH22">
-        <v>1</v>
-      </c>
-      <c r="AI22">
-        <v>1</v>
-      </c>
-      <c r="AJ22">
-        <v>1</v>
-      </c>
-      <c r="AK22">
-        <v>1</v>
-      </c>
-      <c r="AL22">
-        <v>1</v>
-      </c>
-      <c r="AM22">
-        <v>1</v>
-      </c>
-      <c r="AN22">
-        <v>1</v>
-      </c>
-      <c r="AO22">
-        <v>1</v>
-      </c>
-      <c r="AP22">
-        <v>1</v>
-      </c>
-      <c r="AQ22">
-        <v>1</v>
-      </c>
-      <c r="AR22">
-        <v>1</v>
-      </c>
-      <c r="AS22">
-        <v>1</v>
-      </c>
-      <c r="AT22">
-        <v>1</v>
-      </c>
-      <c r="AU22">
-        <v>1</v>
-      </c>
-      <c r="AV22">
-        <v>1</v>
-      </c>
-      <c r="AW22">
-        <v>1</v>
-      </c>
-      <c r="AX22">
-        <v>1</v>
-      </c>
-      <c r="AY22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -4088,68 +2798,8 @@
       <c r="AE23">
         <v>1</v>
       </c>
-      <c r="AF23">
-        <v>1</v>
-      </c>
-      <c r="AG23">
-        <v>1</v>
-      </c>
-      <c r="AH23">
-        <v>1</v>
-      </c>
-      <c r="AI23">
-        <v>1</v>
-      </c>
-      <c r="AJ23">
-        <v>1</v>
-      </c>
-      <c r="AK23">
-        <v>1</v>
-      </c>
-      <c r="AL23">
-        <v>1</v>
-      </c>
-      <c r="AM23">
-        <v>1</v>
-      </c>
-      <c r="AN23">
-        <v>1</v>
-      </c>
-      <c r="AO23">
-        <v>1</v>
-      </c>
-      <c r="AP23">
-        <v>1</v>
-      </c>
-      <c r="AQ23">
-        <v>1</v>
-      </c>
-      <c r="AR23">
-        <v>1</v>
-      </c>
-      <c r="AS23">
-        <v>1</v>
-      </c>
-      <c r="AT23">
-        <v>1</v>
-      </c>
-      <c r="AU23">
-        <v>1</v>
-      </c>
-      <c r="AV23">
-        <v>1</v>
-      </c>
-      <c r="AW23">
-        <v>1</v>
-      </c>
-      <c r="AX23">
-        <v>1</v>
-      </c>
-      <c r="AY23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
@@ -4243,68 +2893,8 @@
       <c r="AE24">
         <v>1</v>
       </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
-      <c r="AG24">
-        <v>1</v>
-      </c>
-      <c r="AH24">
-        <v>1</v>
-      </c>
-      <c r="AI24">
-        <v>1</v>
-      </c>
-      <c r="AJ24">
-        <v>1</v>
-      </c>
-      <c r="AK24">
-        <v>1</v>
-      </c>
-      <c r="AL24">
-        <v>1</v>
-      </c>
-      <c r="AM24">
-        <v>1</v>
-      </c>
-      <c r="AN24">
-        <v>1</v>
-      </c>
-      <c r="AO24">
-        <v>1</v>
-      </c>
-      <c r="AP24">
-        <v>1</v>
-      </c>
-      <c r="AQ24">
-        <v>1</v>
-      </c>
-      <c r="AR24">
-        <v>1</v>
-      </c>
-      <c r="AS24">
-        <v>1</v>
-      </c>
-      <c r="AT24">
-        <v>1</v>
-      </c>
-      <c r="AU24">
-        <v>1</v>
-      </c>
-      <c r="AV24">
-        <v>1</v>
-      </c>
-      <c r="AW24">
-        <v>1</v>
-      </c>
-      <c r="AX24">
-        <v>1</v>
-      </c>
-      <c r="AY24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
@@ -4396,66 +2986,6 @@
         <v>1</v>
       </c>
       <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AG25">
-        <v>1</v>
-      </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AI25">
-        <v>1</v>
-      </c>
-      <c r="AJ25">
-        <v>1</v>
-      </c>
-      <c r="AK25">
-        <v>1</v>
-      </c>
-      <c r="AL25">
-        <v>1</v>
-      </c>
-      <c r="AM25">
-        <v>1</v>
-      </c>
-      <c r="AN25">
-        <v>1</v>
-      </c>
-      <c r="AO25">
-        <v>1</v>
-      </c>
-      <c r="AP25">
-        <v>1</v>
-      </c>
-      <c r="AQ25">
-        <v>1</v>
-      </c>
-      <c r="AR25">
-        <v>1</v>
-      </c>
-      <c r="AS25">
-        <v>1</v>
-      </c>
-      <c r="AT25">
-        <v>1</v>
-      </c>
-      <c r="AU25">
-        <v>1</v>
-      </c>
-      <c r="AV25">
-        <v>1</v>
-      </c>
-      <c r="AW25">
-        <v>1</v>
-      </c>
-      <c r="AX25">
-        <v>1</v>
-      </c>
-      <c r="AY25">
         <v>1</v>
       </c>
     </row>
@@ -4469,14 +2999,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -4570,68 +3100,8 @@
       <c r="AE1" s="3">
         <v>2050</v>
       </c>
-      <c r="AF1" s="3">
-        <v>2051</v>
-      </c>
-      <c r="AG1" s="3">
-        <v>2052</v>
-      </c>
-      <c r="AH1" s="3">
-        <v>2053</v>
-      </c>
-      <c r="AI1" s="3">
-        <v>2054</v>
-      </c>
-      <c r="AJ1" s="3">
-        <v>2055</v>
-      </c>
-      <c r="AK1" s="3">
-        <v>2056</v>
-      </c>
-      <c r="AL1" s="3">
-        <v>2057</v>
-      </c>
-      <c r="AM1" s="3">
-        <v>2058</v>
-      </c>
-      <c r="AN1" s="3">
-        <v>2059</v>
-      </c>
-      <c r="AO1" s="3">
-        <v>2060</v>
-      </c>
-      <c r="AP1" s="3">
-        <v>2061</v>
-      </c>
-      <c r="AQ1" s="3">
-        <v>2062</v>
-      </c>
-      <c r="AR1" s="3">
-        <v>2063</v>
-      </c>
-      <c r="AS1" s="3">
-        <v>2064</v>
-      </c>
-      <c r="AT1" s="3">
-        <v>2065</v>
-      </c>
-      <c r="AU1" s="3">
-        <v>2066</v>
-      </c>
-      <c r="AV1" s="3">
-        <v>2067</v>
-      </c>
-      <c r="AW1" s="3">
-        <v>2068</v>
-      </c>
-      <c r="AX1" s="3">
-        <v>2069</v>
-      </c>
-      <c r="AY1" s="3">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4725,68 +3195,8 @@
       <c r="AE2">
         <v>0</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4880,68 +3290,8 @@
       <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -5035,68 +3385,8 @@
       <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -5190,223 +3480,103 @@
       <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AG6">
-        <v>1</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-      <c r="AJ6">
-        <v>1</v>
-      </c>
-      <c r="AK6">
-        <v>1</v>
-      </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AM6">
-        <v>1</v>
-      </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
-      <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6">
-        <v>1</v>
-      </c>
-      <c r="AQ6">
-        <v>1</v>
-      </c>
-      <c r="AR6">
-        <v>1</v>
-      </c>
-      <c r="AS6">
-        <v>1</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>1</v>
-      </c>
-      <c r="AV6">
-        <v>1</v>
-      </c>
-      <c r="AW6">
-        <v>1</v>
-      </c>
-      <c r="AX6">
-        <v>1</v>
-      </c>
-      <c r="AY6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5500,68 +3670,8 @@
       <c r="AE7">
         <v>1</v>
       </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AG7">
-        <v>1</v>
-      </c>
-      <c r="AH7">
-        <v>1</v>
-      </c>
-      <c r="AI7">
-        <v>1</v>
-      </c>
-      <c r="AJ7">
-        <v>1</v>
-      </c>
-      <c r="AK7">
-        <v>1</v>
-      </c>
-      <c r="AL7">
-        <v>1</v>
-      </c>
-      <c r="AM7">
-        <v>1</v>
-      </c>
-      <c r="AN7">
-        <v>1</v>
-      </c>
-      <c r="AO7">
-        <v>1</v>
-      </c>
-      <c r="AP7">
-        <v>1</v>
-      </c>
-      <c r="AQ7">
-        <v>1</v>
-      </c>
-      <c r="AR7">
-        <v>1</v>
-      </c>
-      <c r="AS7">
-        <v>1</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>1</v>
-      </c>
-      <c r="AV7">
-        <v>1</v>
-      </c>
-      <c r="AW7">
-        <v>1</v>
-      </c>
-      <c r="AX7">
-        <v>1</v>
-      </c>
-      <c r="AY7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -5655,68 +3765,8 @@
       <c r="AE8">
         <v>1</v>
       </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-      <c r="AH8">
-        <v>1</v>
-      </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-      <c r="AJ8">
-        <v>1</v>
-      </c>
-      <c r="AK8">
-        <v>1</v>
-      </c>
-      <c r="AL8">
-        <v>1</v>
-      </c>
-      <c r="AM8">
-        <v>1</v>
-      </c>
-      <c r="AN8">
-        <v>1</v>
-      </c>
-      <c r="AO8">
-        <v>1</v>
-      </c>
-      <c r="AP8">
-        <v>1</v>
-      </c>
-      <c r="AQ8">
-        <v>1</v>
-      </c>
-      <c r="AR8">
-        <v>1</v>
-      </c>
-      <c r="AS8">
-        <v>1</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-      <c r="AV8">
-        <v>1</v>
-      </c>
-      <c r="AW8">
-        <v>1</v>
-      </c>
-      <c r="AX8">
-        <v>1</v>
-      </c>
-      <c r="AY8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -5810,68 +3860,8 @@
       <c r="AE9">
         <v>1</v>
       </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-      <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9">
-        <v>1</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
-      <c r="AK9">
-        <v>1</v>
-      </c>
-      <c r="AL9">
-        <v>1</v>
-      </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
-      <c r="AN9">
-        <v>1</v>
-      </c>
-      <c r="AO9">
-        <v>1</v>
-      </c>
-      <c r="AP9">
-        <v>1</v>
-      </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
-      <c r="AR9">
-        <v>1</v>
-      </c>
-      <c r="AS9">
-        <v>1</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>1</v>
-      </c>
-      <c r="AV9">
-        <v>1</v>
-      </c>
-      <c r="AW9">
-        <v>1</v>
-      </c>
-      <c r="AX9">
-        <v>1</v>
-      </c>
-      <c r="AY9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -5965,68 +3955,8 @@
       <c r="AE10">
         <v>0</v>
       </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>0</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -6120,68 +4050,8 @@
       <c r="AE11">
         <v>1</v>
       </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-      <c r="AH11">
-        <v>1</v>
-      </c>
-      <c r="AI11">
-        <v>1</v>
-      </c>
-      <c r="AJ11">
-        <v>1</v>
-      </c>
-      <c r="AK11">
-        <v>1</v>
-      </c>
-      <c r="AL11">
-        <v>1</v>
-      </c>
-      <c r="AM11">
-        <v>1</v>
-      </c>
-      <c r="AN11">
-        <v>1</v>
-      </c>
-      <c r="AO11">
-        <v>1</v>
-      </c>
-      <c r="AP11">
-        <v>1</v>
-      </c>
-      <c r="AQ11">
-        <v>1</v>
-      </c>
-      <c r="AR11">
-        <v>1</v>
-      </c>
-      <c r="AS11">
-        <v>1</v>
-      </c>
-      <c r="AT11">
-        <v>1</v>
-      </c>
-      <c r="AU11">
-        <v>1</v>
-      </c>
-      <c r="AV11">
-        <v>1</v>
-      </c>
-      <c r="AW11">
-        <v>1</v>
-      </c>
-      <c r="AX11">
-        <v>1</v>
-      </c>
-      <c r="AY11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -6275,68 +4145,8 @@
       <c r="AE12">
         <v>0</v>
       </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -6430,223 +4240,133 @@
       <c r="AE13">
         <v>0</v>
       </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14">
+        <f>B2</f>
         <v>0</v>
       </c>
       <c r="C14">
+        <f t="shared" ref="C14:AE14" si="0">C2</f>
         <v>0</v>
       </c>
       <c r="D14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -6740,68 +4460,8 @@
       <c r="AE15">
         <v>1</v>
       </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>1</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
-      <c r="AK15">
-        <v>1</v>
-      </c>
-      <c r="AL15">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>1</v>
-      </c>
-      <c r="AN15">
-        <v>1</v>
-      </c>
-      <c r="AO15">
-        <v>1</v>
-      </c>
-      <c r="AP15">
-        <v>1</v>
-      </c>
-      <c r="AQ15">
-        <v>1</v>
-      </c>
-      <c r="AR15">
-        <v>1</v>
-      </c>
-      <c r="AS15">
-        <v>1</v>
-      </c>
-      <c r="AT15">
-        <v>1</v>
-      </c>
-      <c r="AU15">
-        <v>1</v>
-      </c>
-      <c r="AV15">
-        <v>1</v>
-      </c>
-      <c r="AW15">
-        <v>1</v>
-      </c>
-      <c r="AX15">
-        <v>1</v>
-      </c>
-      <c r="AY15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -6895,68 +4555,8 @@
       <c r="AE16">
         <v>0</v>
       </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7050,68 +4650,8 @@
       <c r="AE17">
         <v>0</v>
       </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -7205,68 +4745,8 @@
       <c r="AE18">
         <v>0</v>
       </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AI18">
-        <v>0</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>0</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7360,68 +4840,8 @@
       <c r="AE19">
         <v>0</v>
       </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -7515,68 +4935,8 @@
       <c r="AE20">
         <v>0</v>
       </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -7670,68 +5030,8 @@
       <c r="AE21">
         <v>0</v>
       </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -7825,68 +5125,8 @@
       <c r="AE22">
         <v>0</v>
       </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>0</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -7980,375 +5220,195 @@
       <c r="AE23">
         <v>0</v>
       </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>0</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2704A86-BF7B-4C73-BDF4-A433010F241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F768C5D-7BEF-4A35-8B5D-D3FE3CF7D727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CQSD" sheetId="2" r:id="rId2"/>
-    <sheet name="RQSD" sheetId="3" r:id="rId3"/>
+    <sheet name="RQSD-CQSD" sheetId="2" r:id="rId2"/>
+    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -512,22 +511,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,35 +534,35 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
   </sheetData>
@@ -577,14 +576,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BA25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -678,8 +677,74 @@
       <c r="AE1" s="3">
         <v>2050</v>
       </c>
+      <c r="AF1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>2052</v>
+      </c>
+      <c r="AH1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AI1" s="3">
+        <v>2054</v>
+      </c>
+      <c r="AJ1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>2056</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>2058</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>2060</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>2062</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>2064</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2065</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>2066</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2067</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>2068</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2069</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>2070</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>2071</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>2072</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -773,8 +838,74 @@
       <c r="AE2">
         <v>0</v>
       </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -868,8 +999,74 @@
       <c r="AE3">
         <v>0</v>
       </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -963,8 +1160,74 @@
       <c r="AE4">
         <v>0</v>
       </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1058,8 +1321,74 @@
       <c r="AE5">
         <v>1</v>
       </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BA5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1153,8 +1482,74 @@
       <c r="AE6">
         <v>1</v>
       </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1248,8 +1643,74 @@
       <c r="AE7">
         <v>1</v>
       </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BA7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1343,8 +1804,74 @@
       <c r="AE8">
         <v>1</v>
       </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1438,8 +1965,74 @@
       <c r="AE9">
         <v>1</v>
       </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>1</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <v>1</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
+      <c r="BA9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1533,8 +2126,74 @@
       <c r="AE10">
         <v>1</v>
       </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <v>1</v>
+      </c>
+      <c r="AT10">
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <v>1</v>
+      </c>
+      <c r="AW10">
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <v>1</v>
+      </c>
+      <c r="AZ10">
+        <v>1</v>
+      </c>
+      <c r="BA10">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1628,8 +2287,74 @@
       <c r="AE11">
         <v>1</v>
       </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11">
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+      <c r="AZ11">
+        <v>1</v>
+      </c>
+      <c r="BA11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1723,8 +2448,74 @@
       <c r="AE12">
         <v>0</v>
       </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1818,8 +2609,74 @@
       <c r="AE13">
         <v>0</v>
       </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1943,8 +2800,96 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AF14">
+        <f t="shared" ref="AF14:BA14" si="1">AF2</f>
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2038,8 +2983,74 @@
       <c r="AE15">
         <v>1</v>
       </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15">
+        <v>1</v>
+      </c>
+      <c r="AO15">
+        <v>1</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1</v>
+      </c>
+      <c r="AS15">
+        <v>1</v>
+      </c>
+      <c r="AT15">
+        <v>1</v>
+      </c>
+      <c r="AU15">
+        <v>1</v>
+      </c>
+      <c r="AV15">
+        <v>1</v>
+      </c>
+      <c r="AW15">
+        <v>1</v>
+      </c>
+      <c r="AX15">
+        <v>1</v>
+      </c>
+      <c r="AY15">
+        <v>1</v>
+      </c>
+      <c r="AZ15">
+        <v>1</v>
+      </c>
+      <c r="BA15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2133,8 +3144,74 @@
       <c r="AE16">
         <v>0</v>
       </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2228,8 +3305,74 @@
       <c r="AE17">
         <v>0</v>
       </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2323,8 +3466,74 @@
       <c r="AE18">
         <v>0</v>
       </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2418,8 +3627,74 @@
       <c r="AE19">
         <v>1</v>
       </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+      <c r="AM19">
+        <v>1</v>
+      </c>
+      <c r="AN19">
+        <v>1</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>1</v>
+      </c>
+      <c r="AQ19">
+        <v>1</v>
+      </c>
+      <c r="AR19">
+        <v>1</v>
+      </c>
+      <c r="AS19">
+        <v>1</v>
+      </c>
+      <c r="AT19">
+        <v>1</v>
+      </c>
+      <c r="AU19">
+        <v>1</v>
+      </c>
+      <c r="AV19">
+        <v>1</v>
+      </c>
+      <c r="AW19">
+        <v>1</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
+      </c>
+      <c r="AY19">
+        <v>1</v>
+      </c>
+      <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BA19">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2513,8 +3788,74 @@
       <c r="AE20">
         <v>1</v>
       </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>1</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+      <c r="AM20">
+        <v>1</v>
+      </c>
+      <c r="AN20">
+        <v>1</v>
+      </c>
+      <c r="AO20">
+        <v>1</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
+        <v>1</v>
+      </c>
+      <c r="AR20">
+        <v>1</v>
+      </c>
+      <c r="AS20">
+        <v>1</v>
+      </c>
+      <c r="AT20">
+        <v>1</v>
+      </c>
+      <c r="AU20">
+        <v>1</v>
+      </c>
+      <c r="AV20">
+        <v>1</v>
+      </c>
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="AX20">
+        <v>1</v>
+      </c>
+      <c r="AY20">
+        <v>1</v>
+      </c>
+      <c r="AZ20">
+        <v>1</v>
+      </c>
+      <c r="BA20">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2608,8 +3949,74 @@
       <c r="AE21">
         <v>1</v>
       </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>1</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+      <c r="AM21">
+        <v>1</v>
+      </c>
+      <c r="AN21">
+        <v>1</v>
+      </c>
+      <c r="AO21">
+        <v>1</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>1</v>
+      </c>
+      <c r="AR21">
+        <v>1</v>
+      </c>
+      <c r="AS21">
+        <v>1</v>
+      </c>
+      <c r="AT21">
+        <v>1</v>
+      </c>
+      <c r="AU21">
+        <v>1</v>
+      </c>
+      <c r="AV21">
+        <v>1</v>
+      </c>
+      <c r="AW21">
+        <v>1</v>
+      </c>
+      <c r="AX21">
+        <v>1</v>
+      </c>
+      <c r="AY21">
+        <v>1</v>
+      </c>
+      <c r="AZ21">
+        <v>1</v>
+      </c>
+      <c r="BA21">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2703,8 +4110,74 @@
       <c r="AE22">
         <v>1</v>
       </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AM22">
+        <v>1</v>
+      </c>
+      <c r="AN22">
+        <v>1</v>
+      </c>
+      <c r="AO22">
+        <v>1</v>
+      </c>
+      <c r="AP22">
+        <v>1</v>
+      </c>
+      <c r="AQ22">
+        <v>1</v>
+      </c>
+      <c r="AR22">
+        <v>1</v>
+      </c>
+      <c r="AS22">
+        <v>1</v>
+      </c>
+      <c r="AT22">
+        <v>1</v>
+      </c>
+      <c r="AU22">
+        <v>1</v>
+      </c>
+      <c r="AV22">
+        <v>1</v>
+      </c>
+      <c r="AW22">
+        <v>1</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="AY22">
+        <v>1</v>
+      </c>
+      <c r="AZ22">
+        <v>1</v>
+      </c>
+      <c r="BA22">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2798,8 +4271,74 @@
       <c r="AE23">
         <v>1</v>
       </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
+        <v>1</v>
+      </c>
+      <c r="AI23">
+        <v>1</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>1</v>
+      </c>
+      <c r="AM23">
+        <v>1</v>
+      </c>
+      <c r="AN23">
+        <v>1</v>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
+        <v>1</v>
+      </c>
+      <c r="AQ23">
+        <v>1</v>
+      </c>
+      <c r="AR23">
+        <v>1</v>
+      </c>
+      <c r="AS23">
+        <v>1</v>
+      </c>
+      <c r="AT23">
+        <v>1</v>
+      </c>
+      <c r="AU23">
+        <v>1</v>
+      </c>
+      <c r="AV23">
+        <v>1</v>
+      </c>
+      <c r="AW23">
+        <v>1</v>
+      </c>
+      <c r="AX23">
+        <v>1</v>
+      </c>
+      <c r="AY23">
+        <v>1</v>
+      </c>
+      <c r="AZ23">
+        <v>1</v>
+      </c>
+      <c r="BA23">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
@@ -2893,8 +4432,74 @@
       <c r="AE24">
         <v>1</v>
       </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
+      <c r="AM24">
+        <v>1</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>1</v>
+      </c>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24">
+        <v>1</v>
+      </c>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+      <c r="AT24">
+        <v>1</v>
+      </c>
+      <c r="AU24">
+        <v>1</v>
+      </c>
+      <c r="AV24">
+        <v>1</v>
+      </c>
+      <c r="AW24">
+        <v>1</v>
+      </c>
+      <c r="AX24">
+        <v>1</v>
+      </c>
+      <c r="AY24">
+        <v>1</v>
+      </c>
+      <c r="AZ24">
+        <v>1</v>
+      </c>
+      <c r="BA24">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
@@ -2986,6 +4591,72 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25">
+        <v>1</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
+        <v>1</v>
+      </c>
+      <c r="AM25">
+        <v>1</v>
+      </c>
+      <c r="AN25">
+        <v>1</v>
+      </c>
+      <c r="AO25">
+        <v>1</v>
+      </c>
+      <c r="AP25">
+        <v>1</v>
+      </c>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25">
+        <v>1</v>
+      </c>
+      <c r="AS25">
+        <v>1</v>
+      </c>
+      <c r="AT25">
+        <v>1</v>
+      </c>
+      <c r="AU25">
+        <v>1</v>
+      </c>
+      <c r="AV25">
+        <v>1</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
+        <v>1</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
+      <c r="BA25">
         <v>1</v>
       </c>
     </row>
@@ -2999,14 +4670,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AZ25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -3100,8 +4771,71 @@
       <c r="AE1" s="3">
         <v>2050</v>
       </c>
+      <c r="AF1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>2052</v>
+      </c>
+      <c r="AH1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AI1" s="3">
+        <v>2054</v>
+      </c>
+      <c r="AJ1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>2056</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>2058</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>2060</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>2062</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>2064</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2065</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>2066</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2067</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>2068</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2069</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>2070</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>2071</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3195,8 +4929,71 @@
       <c r="AE2">
         <v>0</v>
       </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3290,8 +5087,71 @@
       <c r="AE3">
         <v>0</v>
       </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3385,8 +5245,71 @@
       <c r="AE4">
         <v>0</v>
       </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3480,8 +5403,71 @@
       <c r="AE5">
         <v>0</v>
       </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3575,8 +5561,71 @@
       <c r="AE6">
         <v>0</v>
       </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3670,8 +5719,71 @@
       <c r="AE7">
         <v>1</v>
       </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3765,8 +5877,71 @@
       <c r="AE8">
         <v>1</v>
       </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3860,8 +6035,71 @@
       <c r="AE9">
         <v>1</v>
       </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>1</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <v>1</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3955,8 +6193,71 @@
       <c r="AE10">
         <v>0</v>
       </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -4050,8 +6351,71 @@
       <c r="AE11">
         <v>1</v>
       </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11">
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+      <c r="AZ11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -4145,8 +6509,71 @@
       <c r="AE12">
         <v>0</v>
       </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -4240,8 +6667,71 @@
       <c r="AE13">
         <v>0</v>
       </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4365,8 +6855,92 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AF14">
+        <f t="shared" ref="AF14:AZ14" si="1">AF2</f>
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4460,8 +7034,71 @@
       <c r="AE15">
         <v>1</v>
       </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15">
+        <v>1</v>
+      </c>
+      <c r="AO15">
+        <v>1</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1</v>
+      </c>
+      <c r="AS15">
+        <v>1</v>
+      </c>
+      <c r="AT15">
+        <v>1</v>
+      </c>
+      <c r="AU15">
+        <v>1</v>
+      </c>
+      <c r="AV15">
+        <v>1</v>
+      </c>
+      <c r="AW15">
+        <v>1</v>
+      </c>
+      <c r="AX15">
+        <v>1</v>
+      </c>
+      <c r="AY15">
+        <v>1</v>
+      </c>
+      <c r="AZ15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -4555,8 +7192,71 @@
       <c r="AE16">
         <v>0</v>
       </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4650,8 +7350,71 @@
       <c r="AE17">
         <v>0</v>
       </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -4745,8 +7508,71 @@
       <c r="AE18">
         <v>0</v>
       </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4840,8 +7666,71 @@
       <c r="AE19">
         <v>0</v>
       </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4935,8 +7824,71 @@
       <c r="AE20">
         <v>0</v>
       </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -5030,8 +7982,71 @@
       <c r="AE21">
         <v>0</v>
       </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -5125,8 +8140,71 @@
       <c r="AE22">
         <v>0</v>
       </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -5220,8 +8298,71 @@
       <c r="AE23">
         <v>0</v>
       </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
@@ -5315,8 +8456,71 @@
       <c r="AE24">
         <v>1</v>
       </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
+      <c r="AM24">
+        <v>1</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>1</v>
+      </c>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24">
+        <v>1</v>
+      </c>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+      <c r="AT24">
+        <v>1</v>
+      </c>
+      <c r="AU24">
+        <v>1</v>
+      </c>
+      <c r="AV24">
+        <v>1</v>
+      </c>
+      <c r="AW24">
+        <v>1</v>
+      </c>
+      <c r="AX24">
+        <v>1</v>
+      </c>
+      <c r="AY24">
+        <v>1</v>
+      </c>
+      <c r="AZ24">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
@@ -5408,6 +8612,69 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25">
+        <v>1</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
+        <v>1</v>
+      </c>
+      <c r="AM25">
+        <v>1</v>
+      </c>
+      <c r="AN25">
+        <v>1</v>
+      </c>
+      <c r="AO25">
+        <v>1</v>
+      </c>
+      <c r="AP25">
+        <v>1</v>
+      </c>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25">
+        <v>1</v>
+      </c>
+      <c r="AS25">
+        <v>1</v>
+      </c>
+      <c r="AT25">
+        <v>1</v>
+      </c>
+      <c r="AU25">
+        <v>1</v>
+      </c>
+      <c r="AV25">
+        <v>1</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
+        <v>1</v>
+      </c>
+      <c r="AZ25">
         <v>1</v>
       </c>
     </row>
